--- a/data/trans_dic/P3A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -649,62 +649,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>73,2%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,18</t>
+          <t>30,04; 35,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,21</t>
+          <t>32,2; 38,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,25</t>
+          <t>38,78; 45,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>52,2; 60,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>84,7; 88,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>80,63; 85,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,22</t>
+          <t>81,97; 87,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,13</t>
+          <t>82,82; 86,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,08</t>
+          <t>60,95; 64,92</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,09</t>
+          <t>60,78; 64,92</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>64,28; 68,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,09</t>
+          <t>71,09; 75,27</t>
         </is>
       </c>
     </row>
@@ -789,62 +789,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>76,36%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>30,22; 34,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>42,75; 47,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>51,43; 55,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>40,61; 67,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>81,48; 85,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>83,04; 86,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>87,55; 90,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,07</t>
+          <t>92,28; 95,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>55,28; 58,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>62,32; 65,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,05</t>
+          <t>69,53; 72,39</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,04</t>
+          <t>62,52; 81,8</t>
         </is>
       </c>
     </row>
@@ -929,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>81,72%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>37,81; 46,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,44</t>
+          <t>49,28; 59,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>61,6; 70,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>68,84; 76,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,42</t>
+          <t>75,34; 83,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,46</t>
+          <t>77,01; 84,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,37</t>
+          <t>83,32; 89,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>87,57; 92,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>55,96; 62,08</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,23</t>
+          <t>64,24; 70,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>73,5; 78,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,11</t>
+          <t>79,13; 83,86</t>
         </is>
       </c>
     </row>
@@ -1069,62 +1069,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>76,78%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>32,51; 35,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>41,98; 45,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>51,4; 54,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>46,48; 66,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>82,71; 85,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>82,3; 84,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>86,15; 88,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,04</t>
+          <t>90,26; 92,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,03</t>
+          <t>58,32; 60,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,03</t>
+          <t>62,81; 65,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,03</t>
+          <t>69,52; 71,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,02</t>
+          <t>67,67; 80,08</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1368,62 +1368,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>334</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>327</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>319</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>377</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>767</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1586</t>
         </is>
       </c>
     </row>
@@ -1436,62 +1436,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>339466</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>345486</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>319574</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>288546</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1138553</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1108436</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>841491</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>641382</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1478019</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1453923</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1161065</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>929928</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1907</t>
+          <t>309889; 369181</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2059</t>
+          <t>313454; 376906</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1899</t>
+          <t>291508; 345663</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1429</t>
+          <t>268785; 310912</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1955</t>
+          <t>1113082; 1162558</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2059</t>
+          <t>1077830; 1136388</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2139</t>
+          <t>813681; 865449</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1016</t>
+          <t>625679; 656571</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1934</t>
+          <t>1429752; 1522874</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 2060</t>
+          <t>1404288; 1499819</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 2030</t>
+          <t>1121232; 1201449</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 1151</t>
+          <t>903201; 956313</t>
         </is>
       </c>
     </row>
@@ -1576,62 +1576,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>510</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>830</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1690</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2783</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4123</t>
         </is>
       </c>
     </row>
@@ -1644,62 +1644,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>550294</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>886184</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1112341</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1354415</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1321570</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1489202</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1766353</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2101599</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1871864</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2375386</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2878694</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3456014</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1971</t>
+          <t>511509; 591173</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2031</t>
+          <t>839665; 932405</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2041</t>
+          <t>1065140; 1157094</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2208</t>
+          <t>929677; 1536495</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1960</t>
+          <t>1291712; 1350094</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2064</t>
+          <t>1458888; 1519597</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2000</t>
+          <t>1739126; 1793534</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1471</t>
+          <t>2063978; 2136282</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1967</t>
+          <t>1811924; 1925930</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 2047</t>
+          <t>2318701; 2436606</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2021</t>
+          <t>2820896; 2937093</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 1770</t>
+          <t>2829615; 3702192</t>
         </is>
       </c>
     </row>
@@ -1784,62 +1784,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>215</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>233</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>327</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>500</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>355</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>336</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>453</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>933</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>570</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>569</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>780</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1433</t>
         </is>
       </c>
     </row>
@@ -1852,62 +1852,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>230576</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>261455</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>360088</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>470459</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>377162</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>373183</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>473081</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>597713</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>607739</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>634638</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>833169</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1068172</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2005</t>
+          <t>208493; 255506</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2104</t>
+          <t>237148; 285614</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2092</t>
+          <t>336259; 382142</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1821</t>
+          <t>445163; 492993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2019</t>
+          <t>358063; 394859</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2132</t>
+          <t>353209; 389248</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2001</t>
+          <t>456784; 488418</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 1262</t>
+          <t>578385; 612140</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2014</t>
+          <t>574507; 637337</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 2121</t>
+          <t>603728; 663456</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2048</t>
+          <t>804142; 861752</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 1489</t>
+          <t>1034284; 1096074</t>
         </is>
       </c>
     </row>
@@ -1992,62 +1992,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7142</t>
         </is>
       </c>
     </row>
@@ -2060,62 +2060,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1120336</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1493126</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1792003</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2113420</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2837285</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2970821</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3080925</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3340694</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3957622</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4463947</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4872929</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5454113</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1957</t>
+          <t>1064943; 1177799</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2051</t>
+          <t>1435290; 1551396</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2017</t>
+          <t>1731413; 1850148</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1971</t>
+          <t>1604062; 2294315</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1968</t>
+          <t>2791090; 2877241</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2072</t>
+          <t>2923481; 3012822</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2039</t>
+          <t>3038524; 3122716</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 1311</t>
+          <t>3296788; 3393953</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1963</t>
+          <t>3878149; 4043597</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 2062</t>
+          <t>4378619; 4544182</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 2029</t>
+          <t>4794123; 4949499</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 1566</t>
+          <t>4807089; 5688597</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,14%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,04; 35,78</t>
+          <t>30,21; 35,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,2; 38,71</t>
+          <t>32,4; 38,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38,78; 45,99</t>
+          <t>39,06; 46,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52,2; 60,38</t>
+          <t>52,28; 60,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>84,7; 88,47</t>
+          <t>84,58; 88,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,63; 85,01</t>
+          <t>80,78; 85,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,97; 87,19</t>
+          <t>82,42; 87,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>82,82; 86,9</t>
+          <t>82,96; 86,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>60,95; 64,92</t>
+          <t>61,06; 64,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60,78; 64,92</t>
+          <t>60,65; 64,83</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64,28; 68,88</t>
+          <t>64,2; 68,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>71,09; 75,27</t>
+          <t>71,06; 75,3</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>79,08%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,22; 34,93</t>
+          <t>30,3; 35,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,75; 47,48</t>
+          <t>43,04; 47,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51,43; 55,87</t>
+          <t>51,4; 55,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40,61; 67,12</t>
+          <t>63,06; 67,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,48; 85,16</t>
+          <t>81,6; 85,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,04; 86,5</t>
+          <t>82,86; 86,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,55; 90,29</t>
+          <t>87,45; 90,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>92,28; 95,52</t>
+          <t>91,3; 94,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>55,28; 58,76</t>
+          <t>55,4; 58,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62,32; 65,49</t>
+          <t>62,25; 65,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69,53; 72,39</t>
+          <t>69,35; 72,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>62,52; 81,8</t>
+          <t>77,61; 80,43</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,42%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,81; 46,34</t>
+          <t>37,27; 46,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>49,28; 59,36</t>
+          <t>48,87; 59,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61,6; 70,0</t>
+          <t>61,63; 69,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68,84; 76,24</t>
+          <t>68,56; 75,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>75,34; 83,08</t>
+          <t>75,84; 82,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>77,01; 84,87</t>
+          <t>77,48; 85,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83,32; 89,09</t>
+          <t>82,79; 89,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>87,57; 92,68</t>
+          <t>87,66; 92,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>55,96; 62,08</t>
+          <t>55,87; 62,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>64,24; 70,59</t>
+          <t>64,5; 70,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73,5; 78,76</t>
+          <t>73,38; 78,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>79,13; 83,86</t>
+          <t>79,19; 83,89</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>78,4%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,51; 35,96</t>
+          <t>32,5; 35,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,98; 45,38</t>
+          <t>41,94; 45,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51,4; 54,92</t>
+          <t>51,52; 54,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46,48; 66,49</t>
+          <t>63,64; 67,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,71; 85,26</t>
+          <t>82,87; 85,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,3; 84,81</t>
+          <t>82,37; 84,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,15; 88,53</t>
+          <t>86,12; 88,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>90,26; 92,92</t>
+          <t>89,68; 91,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58,32; 60,8</t>
+          <t>58,33; 60,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62,81; 65,19</t>
+          <t>62,84; 65,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69,52; 71,78</t>
+          <t>69,48; 71,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67,67; 80,08</t>
+          <t>77,33; 79,47</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288546</t>
+          <t>325784</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>641382</t>
+          <t>698660</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>929928</t>
+          <t>1024444</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>309889; 369181</t>
+          <t>311641; 370987</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>313454; 376906</t>
+          <t>315439; 376132</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>291508; 345663</t>
+          <t>293586; 347475</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>268785; 310912</t>
+          <t>302427; 348613</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1113082; 1162558</t>
+          <t>1111445; 1161041</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1077830; 1136388</t>
+          <t>1079931; 1137487</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>813681; 865449</t>
+          <t>818066; 866945</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>625679; 656571</t>
+          <t>681969; 714918</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1429752; 1522874</t>
+          <t>1432270; 1520434</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1404288; 1499819</t>
+          <t>1401177; 1497925</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1121232; 1201449</t>
+          <t>1119803; 1199005</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>903201; 956313</t>
+          <t>995278; 1054637</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1354415</t>
+          <t>1461796</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2101599</t>
+          <t>2017501</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3456014</t>
+          <t>3479297</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>511509; 591173</t>
+          <t>512919; 593314</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>839665; 932405</t>
+          <t>845272; 933546</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1065140; 1157094</t>
+          <t>1064509; 1157720</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>929677; 1536495</t>
+          <t>1405871; 1509290</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1291712; 1350094</t>
+          <t>1293522; 1350243</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1458888; 1519597</t>
+          <t>1455674; 1519038</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1739126; 1793534</t>
+          <t>1737003; 1794273</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2063978; 2136282</t>
+          <t>1981361; 2043463</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1811924; 1925930</t>
+          <t>1815993; 1929927</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2318701; 2436606</t>
+          <t>2316159; 2433832</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2820896; 2937093</t>
+          <t>2813715; 2927877</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2829615; 3702192</t>
+          <t>3414702; 3538790</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>470459</t>
+          <t>514603</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>597713</t>
+          <t>663039</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1068172</t>
+          <t>1177642</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>208493; 255506</t>
+          <t>205534; 253667</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>237148; 285614</t>
+          <t>235143; 284420</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>336259; 382142</t>
+          <t>336448; 382112</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>445163; 492993</t>
+          <t>487830; 540067</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>358063; 394859</t>
+          <t>360433; 393750</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>353209; 389248</t>
+          <t>355335; 389958</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>456784; 488418</t>
+          <t>453874; 488352</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>578385; 612140</t>
+          <t>644181; 677799</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>574507; 637337</t>
+          <t>573633; 639476</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>603728; 663456</t>
+          <t>606220; 664265</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>804142; 861752</t>
+          <t>802824; 861487</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1034284; 1096074</t>
+          <t>1145388; 1213431</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2113420</t>
+          <t>2302183</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3340694</t>
+          <t>3379200</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5454113</t>
+          <t>5681383</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1064943; 1177799</t>
+          <t>1064692; 1178098</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1435290; 1551396</t>
+          <t>1433744; 1556234</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1731413; 1850148</t>
+          <t>1735548; 1849552</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1604062; 2294315</t>
+          <t>2239892; 2364467</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2791090; 2877241</t>
+          <t>2796494; 2881418</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2923481; 3012822</t>
+          <t>2926020; 3013354</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3038524; 3122716</t>
+          <t>3037610; 3120922</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3296788; 3393953</t>
+          <t>3342360; 3417286</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3878149; 4043597</t>
+          <t>3879112; 4037308</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4378619; 4544182</t>
+          <t>4380828; 4545543</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4794123; 4949499</t>
+          <t>4791311; 4941583</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4807089; 5688597</t>
+          <t>5603862; 5759016</t>
         </is>
       </c>
     </row>
